--- a/artfynd/A 54582-2022 artfynd.xlsx
+++ b/artfynd/A 54582-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119681222</v>
+        <v>119681232</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555082</v>
+        <v>555271</v>
       </c>
       <c r="R3" t="n">
-        <v>7077843</v>
+        <v>7077619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119681232</v>
+        <v>119681215</v>
       </c>
       <c r="B4" t="n">
         <v>90562</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555271</v>
+        <v>555112</v>
       </c>
       <c r="R4" t="n">
-        <v>7077619</v>
+        <v>7077882</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119681215</v>
+        <v>119681222</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555112</v>
+        <v>555082</v>
       </c>
       <c r="R6" t="n">
-        <v>7077882</v>
+        <v>7077843</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 54582-2022 artfynd.xlsx
+++ b/artfynd/A 54582-2022 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119681215</v>
+        <v>119681258</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555112</v>
+        <v>554757</v>
       </c>
       <c r="R4" t="n">
-        <v>7077882</v>
+        <v>7078204</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119681258</v>
+        <v>119681215</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554757</v>
+        <v>555112</v>
       </c>
       <c r="R5" t="n">
-        <v>7078204</v>
+        <v>7077882</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 54582-2022 artfynd.xlsx
+++ b/artfynd/A 54582-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119681232</v>
+        <v>119681222</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555271</v>
+        <v>555082</v>
       </c>
       <c r="R3" t="n">
-        <v>7077619</v>
+        <v>7077843</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119681258</v>
+        <v>119681215</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554757</v>
+        <v>555112</v>
       </c>
       <c r="R4" t="n">
-        <v>7078204</v>
+        <v>7077882</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119681215</v>
+        <v>119681232</v>
       </c>
       <c r="B5" t="n">
         <v>90562</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555112</v>
+        <v>555271</v>
       </c>
       <c r="R5" t="n">
-        <v>7077882</v>
+        <v>7077619</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119681222</v>
+        <v>119681240</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555082</v>
+        <v>555060</v>
       </c>
       <c r="R6" t="n">
-        <v>7077843</v>
+        <v>7078059</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119681240</v>
+        <v>119681258</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555060</v>
+        <v>554757</v>
       </c>
       <c r="R7" t="n">
-        <v>7078059</v>
+        <v>7078204</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 54582-2022 artfynd.xlsx
+++ b/artfynd/A 54582-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119681222</v>
+        <v>119681240</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555082</v>
+        <v>555060</v>
       </c>
       <c r="R3" t="n">
-        <v>7077843</v>
+        <v>7078059</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119681232</v>
+        <v>119681222</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555271</v>
+        <v>555082</v>
       </c>
       <c r="R5" t="n">
-        <v>7077619</v>
+        <v>7077843</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119681240</v>
+        <v>119681232</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555060</v>
+        <v>555271</v>
       </c>
       <c r="R6" t="n">
-        <v>7078059</v>
+        <v>7077619</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 54582-2022 artfynd.xlsx
+++ b/artfynd/A 54582-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119681244</v>
+        <v>119681215</v>
       </c>
       <c r="B2" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554715</v>
+        <v>555112</v>
       </c>
       <c r="R2" t="n">
-        <v>7078274</v>
+        <v>7077882</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119681240</v>
+        <v>119681232</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555060</v>
+        <v>555271</v>
       </c>
       <c r="R3" t="n">
-        <v>7078059</v>
+        <v>7077619</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119681215</v>
+        <v>119681258</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555112</v>
+        <v>554757</v>
       </c>
       <c r="R4" t="n">
-        <v>7077882</v>
+        <v>7078204</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119681222</v>
+        <v>119681244</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555082</v>
+        <v>554715</v>
       </c>
       <c r="R5" t="n">
-        <v>7077843</v>
+        <v>7078274</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119681232</v>
+        <v>119681222</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555271</v>
+        <v>555082</v>
       </c>
       <c r="R6" t="n">
-        <v>7077619</v>
+        <v>7077843</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,112 +1177,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>119681258</v>
-      </c>
-      <c r="B7" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Kanan, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>554757</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7078204</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Maria Johansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54582-2022 artfynd.xlsx
+++ b/artfynd/A 54582-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119681215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119681232</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119681258</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119681244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119681222</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>